--- a/Excel9to10/WhatIf.xlsx
+++ b/Excel9to10/WhatIf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E6F24F-DB16-456C-A7E6-5228159E883F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16C4468-D7DF-4065-8A6E-25E0B44A90D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{50DE6D63-8DAA-4E08-90BB-BF14336C7275}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{50DE6D63-8DAA-4E08-90BB-BF14336C7275}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioManager" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>Product</t>
   </si>
@@ -107,9 +110,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Percentage</t>
-  </si>
-  <si>
     <t>Parth</t>
   </si>
   <si>
@@ -167,7 +167,7 @@
     <t>formula</t>
   </si>
   <si>
-    <t>QTY</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -362,9 +362,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -402,7 +402,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -508,7 +508,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -650,7 +650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -659,13 +659,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6718082E-B30D-4ECD-A520-C90D9B73636F}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -673,7 +673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -681,7 +681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -689,7 +689,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -698,61 +698,55 @@
         <v>500000</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4">
         <f>B4*B5</f>
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4">
         <f>B4-B6</f>
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
   </sheetData>
-  <scenarios current="4" show="4" sqref="B7">
-    <scenario name="Jan" locked="1" count="1" user="jitender sarswat" comment="Created by jitender sarswat on 12-12-2025_x000a_Modified by jitender sarswat on 12-12-2025">
+  <scenarios current="1" show="1" sqref="B7">
+    <scenario name="Jan" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
       <inputCells r="B5" val="0.2" numFmtId="9"/>
     </scenario>
-    <scenario name="Feb" locked="1" count="1" user="jitender sarswat" comment="Created by jitender sarswat on 12-12-2025">
-      <inputCells r="B5" val="0.15" numFmtId="9"/>
+    <scenario name="Feb" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
+      <inputCells r="B5" val="0.4" numFmtId="9"/>
     </scenario>
-    <scenario name="March" locked="1" count="1" user="jitender sarswat" comment="Created by jitender sarswat on 12-12-2025">
-      <inputCells r="B5" val="0.08" numFmtId="9"/>
-    </scenario>
-    <scenario name="April" locked="1" count="1" user="jitender sarswat" comment="Created by jitender sarswat on 12-12-2025">
-      <inputCells r="B5" val="0.3" numFmtId="9"/>
-    </scenario>
-    <scenario name="May" locked="1" count="1" user="jitender sarswat" comment="Created by jitender sarswat on 12-12-2025">
-      <inputCells r="B5" val="0.5" numFmtId="9"/>
+    <scenario name="March" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
+      <inputCells r="B5" val="0.65" numFmtId="9"/>
     </scenario>
   </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -762,20 +756,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B5177A-35E5-477A-ADCE-D6D92A37EC33}">
   <dimension ref="A1:W25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.21875" customWidth="1"/>
-    <col min="23" max="23" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.28515625" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -789,22 +783,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="9">
         <v>20</v>
       </c>
       <c r="C2" s="10">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D2" s="10">
         <f>B2*C2</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
@@ -826,19 +820,17 @@
       <c r="I7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C8" s="9" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="C8" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="D8" s="9">
         <v>78</v>
       </c>
       <c r="E8" s="9">
-        <v>41</v>
+        <v>71.000000000000028</v>
       </c>
       <c r="F8" s="9">
         <v>59</v>
@@ -851,31 +843,31 @@
       </c>
       <c r="I8" s="9">
         <f>SUM(D8:H8)</f>
-        <v>349.99999999999994</v>
+        <v>380</v>
       </c>
       <c r="J8" s="11"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="V12" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W12" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="V13" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W13" s="10">
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="F14" s="8" t="s">
         <v>10</v>
       </c>
@@ -895,16 +887,16 @@
         <v>14</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W14" s="10">
         <v>24000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="F15" s="9" t="s">
         <v>15</v>
       </c>
@@ -912,7 +904,7 @@
         <v>60000</v>
       </c>
       <c r="H15" s="10">
-        <v>33870.739438198871</v>
+        <v>46935.371756546403</v>
       </c>
       <c r="I15" s="11">
         <v>0.03</v>
@@ -925,78 +917,78 @@
       </c>
       <c r="L15" s="15">
         <f>PMT(I15,J15,H15-G15)</f>
-        <v>6000.0009357083545</v>
+        <v>3000</v>
       </c>
       <c r="V15" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W15" s="10">
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="V16" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W16" s="10">
         <v>36000</v>
       </c>
     </row>
-    <row r="17" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V17" s="12"/>
       <c r="W17" s="7"/>
     </row>
-    <row r="18" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V18" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W18" s="10">
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V19" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W19" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V20" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W20" s="10">
         <v>37500</v>
       </c>
     </row>
-    <row r="21" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V21" s="12"/>
       <c r="W21" s="7"/>
     </row>
-    <row r="22" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="22:23" ht="30" x14ac:dyDescent="0.25">
       <c r="V22" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W22" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V23" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W23" s="10">
         <v>937500</v>
       </c>
     </row>
-    <row r="24" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V24" s="12"/>
       <c r="W24" s="7"/>
     </row>
-    <row r="25" spans="22:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="22:23" x14ac:dyDescent="0.25">
       <c r="V25" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W25" s="10">
         <v>901500</v>
@@ -1010,21 +1002,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77E5C4B-1A49-425D-9C1F-2D40DA500523}">
   <dimension ref="A1:M33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1032,7 +1024,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1040,29 +1032,29 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="21">
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="20">
         <f>B2*B3*B4</f>
         <v>7500</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G9" s="23">
         <f>B5</f>
         <v>7500</v>
@@ -1086,7 +1078,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G10" s="9">
         <v>100</v>
       </c>
@@ -1110,7 +1102,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G11" s="9">
         <v>200</v>
       </c>
@@ -1133,10 +1125,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G12" s="9">
         <v>250</v>
       </c>
@@ -1159,7 +1148,7 @@
         <v>8750</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G13" s="9">
         <v>300</v>
       </c>
@@ -1182,12 +1171,12 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="9">
         <v>450</v>
@@ -1211,7 +1200,7 @@
         <v>15749.999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="17">
         <f>B5</f>
@@ -1239,16 +1228,16 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>100</v>
       </c>
       <c r="B16" s="9">
-        <f t="dataTable" ref="B16:B21" dt2D="0" dtr="0" r1="B2"/>
+        <f t="dataTable" ref="B16:B21" dt2D="0" dtr="0" r1="B2" ca="1"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>200</v>
       </c>
@@ -1256,7 +1245,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>250</v>
       </c>
@@ -1264,7 +1253,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>300</v>
       </c>
@@ -1272,15 +1261,18 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>450</v>
       </c>
       <c r="B20" s="9">
         <v>13500</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>500</v>
       </c>
@@ -1288,30 +1280,30 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25">
         <f>B5</f>
         <v>7500</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="22">
         <v>0.1</v>
       </c>
       <c r="B26" s="19">
-        <f t="dataTable" ref="B26:B29" dt2D="0" dtr="0" r1="B4" ca="1"/>
+        <f t="dataTable" ref="B26:B29" dt2D="0" dtr="0" r1="B4"/>
         <v>1250</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="B27" s="19">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="22">
         <v>0.3</v>
       </c>
@@ -1319,7 +1311,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
         <v>0.4</v>
       </c>
@@ -1327,16 +1319,16 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
     </row>
   </sheetData>

--- a/Excel9to10/WhatIf.xlsx
+++ b/Excel9to10/WhatIf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16C4468-D7DF-4065-8A6E-25E0B44A90D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559C27D6-066C-4D2B-979F-18903C4D54A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{50DE6D63-8DAA-4E08-90BB-BF14336C7275}"/>
   </bookViews>
@@ -362,9 +362,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -402,7 +402,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -508,7 +508,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -650,7 +650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -738,17 +738,6 @@
       <c r="B8" s="2"/>
     </row>
   </sheetData>
-  <scenarios current="1" show="1" sqref="B7">
-    <scenario name="Jan" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
-      <inputCells r="B5" val="0.2" numFmtId="9"/>
-    </scenario>
-    <scenario name="Feb" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
-      <inputCells r="B5" val="0.4" numFmtId="9"/>
-    </scenario>
-    <scenario name="March" locked="1" count="1" user="RWR2" comment="Created by RWR2 on 09-02-2026">
-      <inputCells r="B5" val="0.65" numFmtId="9"/>
-    </scenario>
-  </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -788,14 +777,14 @@
         <v>36</v>
       </c>
       <c r="B2" s="9">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C2" s="10">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D2" s="10">
         <f>B2*C2</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -833,7 +822,7 @@
         <v>71.000000000000028</v>
       </c>
       <c r="F8" s="9">
-        <v>59</v>
+        <v>39.000000000000036</v>
       </c>
       <c r="G8" s="9">
         <v>91.999999999999957</v>
@@ -843,7 +832,7 @@
       </c>
       <c r="I8" s="9">
         <f>SUM(D8:H8)</f>
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="J8" s="11"/>
     </row>
@@ -1233,7 +1222,7 @@
         <v>100</v>
       </c>
       <c r="B16" s="9">
-        <f t="dataTable" ref="B16:B21" dt2D="0" dtr="0" r1="B2" ca="1"/>
+        <f t="dataTable" ref="B16:B21" dt2D="0" dtr="0" r1="B2"/>
         <v>3000</v>
       </c>
     </row>
@@ -1291,7 +1280,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" s="19">
-        <f t="dataTable" ref="B26:B29" dt2D="0" dtr="0" r1="B4"/>
+        <f t="dataTable" ref="B26:B29" dt2D="0" dtr="0" r1="B4" ca="1"/>
         <v>1250</v>
       </c>
     </row>
